--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -4874,7 +4874,7 @@
         <v>113312539</v>
       </c>
       <c r="B36" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -4874,7 +4874,7 @@
         <v>113312539</v>
       </c>
       <c r="B36" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -4874,7 +4874,7 @@
         <v>113312539</v>
       </c>
       <c r="B36" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -4874,7 +4874,7 @@
         <v>113312539</v>
       </c>
       <c r="B36" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -4874,7 +4874,7 @@
         <v>113312539</v>
       </c>
       <c r="B36" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -4874,7 +4874,7 @@
         <v>113312539</v>
       </c>
       <c r="B36" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -4874,7 +4874,7 @@
         <v>113312539</v>
       </c>
       <c r="B36" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23039-2023 artfynd.xlsx
+++ b/artfynd/A 23039-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4871,69 +4871,65 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113312539</v>
+        <v>110521779</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
+        <v>56513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>102118</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lisjökilsskogen/ ca 750 m NV Skinnartorp (knärot), Vstm</t>
+          <t>Skinnartorpsskogen, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561061</v>
+        <v>561240</v>
       </c>
       <c r="R36" t="n">
-        <v>6622817</v>
+        <v>6622755</v>
       </c>
       <c r="S36" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4955,24 +4951,24 @@
           <t>Sura</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>U-Sur-0406</t>
-        </is>
-      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>4 dellokaler m2 bladrosetter,10 pl med rosetter, 2 pl i knopp) koordinaer se AP dålig blomning kanske beroende på sommarens torka (Skinnartorpsskogen)</t>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4981,150 +4977,21 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sören Larsson, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>110521779</v>
-      </c>
-      <c r="B37" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>102118</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Caprimulgus europaeus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Skinnartorpsskogen, Sura sn, Vstm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>561240</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6622755</v>
-      </c>
-      <c r="S37" t="n">
-        <v>50</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Sura</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
           <t>Sören Larsson</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
